--- a/04_DESIGN_TABLES/DesignTable_1501.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_1501.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q52"/>
+  <dimension ref="A1:R52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -504,6 +504,11 @@
           <t>$PRP@OMiSKU</t>
         </is>
       </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3593,24 +3598,56 @@
           <t>1501-16-20-FG</t>
         </is>
       </c>
+      <c r="B51" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="C51" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="D51" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="E51" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="F51" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="H51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I51" t="n">
+        <v>1.315</v>
+      </c>
+      <c r="J51" t="n">
+        <v>1.66</v>
+      </c>
       <c r="K51" t="inlineStr">
         <is>
           <t>1501-16-20-FG</t>
         </is>
       </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>1-11 1/2 (A NPTF) x 1 1/4-11 1/2 (A1 NPSM)</t>
+        </is>
+      </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1501-16-20 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1501-16-20 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): N1@DRIVE: Brennan TFA catalog p.20 table TFA-p020-t01 "1501-FG MP-FPS 90 DEG ELBOW" row 1501-16-20-FG col "L LGTH" = "2.350" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 415.3, page verified True) [Brennan = yes 2026-10-18] - axis crossing to the male NPTF tip (column mapping: REPORT.md, table 1501); M1@DRIVE: Brennan TFA catalog p.20 table TFA-p020-t01 "1501-FG MP-FPS 90 DEG ELBOW" row 1501-16-20-FG col "M LGTH" = "1.730" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 415.3, page verified True) [Brennan = yes 2026-10-18] - axis crossing to the NPSM swivel stem tip (column mapping: REPORT.md, table 1501); W3@HEX: Brennan TFA catalog p.20 table TFA-p020-t01 "1501-FG MP-FPS 90 DEG ELBOW" row 1501-16-20-FG col "M1 LGTH" = "2.150" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 415.3, page verified True) [Brennan = yes 2026-10-18] - axis crossing to the swivel-nut face (column mapping: REPORT.md, table 1501); CHEX@HEX: Brennan TFA catalog p.20 table TFA-p020-t01 "1501-FG MP-FPS 90 DEG ELBOW" row 1501-16-20-FG col "C HEX" = "1.875" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 415.3, page verified True) [Brennan = yes 2026-10-18] - swivel nut hex (column mapping: REPORT.md, table 1501); C1HEX@HEX: Brennan TFA catalog p.20 table TFA-p020-t01 "1501-FG MP-FPS 90 DEG ELBOW" row 1501-16-20-FG col "Y FLATS" = "1.625" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 415.3, page verified True) [Brennan = yes 2026-10-18] - forged body flats (column mapping: REPORT.md, table 1501); D2@BORE: Brennan TFA catalog p.20 table TFA-p020-t01 "1501-FG MP-FPS 90 DEG ELBOW" row 1501-16-20-FG col "A1 DRILL" = "0.938" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 415.3, page verified True) [Brennan = yes 2026-10-18] - male NPTF end drill (column mapping: REPORT.md, table 1501); D@BORE: Brennan TFA catalog p.20 table TFA-p020-t01 "1501-FG MP-FPS 90 DEG ELBOW" row 1501-16-20-FG col "A2 DRILL" = "1.010" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 415.3, page verified True) [Brennan = yes 2026-10-18] - NPSM swivel stem bore (column mapping: REPORT.md, table 1501); THDMAJ_A@DRIVE: end library: pipe OD of the -16 NPTF thread = 1.315 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[16], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A1@DRIVE: end library: pipe OD of the -20 NPSM swivel thread = 1.66 (ASME B1.20.1 pipe OD, ms51500.py NPTF[20]; the value every built 1501 / 1405 / 1502 row carries for its NPSM end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Threads: thread callouts from the part number dashes in the format of the table's other rows; = Brennan TFA-p020-t01 thread columns (A1 NPTF 1-11-1/2, A2 NPSM 1-1/4-11-1/2) and OMi Items Side 1 / 2 / 3 Thread</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1501-16-20 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1501-16-20 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog, end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate)</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -3621,6 +3658,11 @@
       <c r="Q51" t="inlineStr">
         <is>
           <t>1501-16-20-FG</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -3630,24 +3672,56 @@
           <t>1501-20-16-FG</t>
         </is>
       </c>
+      <c r="B52" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="C52" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D52" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="E52" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F52" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="G52" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="I52" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="J52" t="n">
+        <v>1.315</v>
+      </c>
       <c r="K52" t="inlineStr">
         <is>
           <t>1501-20-16-FG</t>
         </is>
       </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>1 1/4-11 1/2 (A NPTF) x 1-11 1/2 (A1 NPSM)</t>
+        </is>
+      </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1501-20-16 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1501-20-16 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): N1@DRIVE: Brennan TFA catalog p.20 table TFA-p020-t01 "1501-FG MP-FPS 90 DEG ELBOW" row 1501-20-16-FG col "L LGTH" = "2.380" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 435.5, page verified True) [Brennan = yes 2026-10-18] - axis crossing to the male NPTF tip (column mapping: REPORT.md, table 1501); M1@DRIVE: Brennan TFA catalog p.20 table TFA-p020-t01 "1501-FG MP-FPS 90 DEG ELBOW" row 1501-20-16-FG col "M LGTH" = "1.700" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 435.5, page verified True) [Brennan = yes 2026-10-18] - axis crossing to the NPSM swivel stem tip (column mapping: REPORT.md, table 1501); W3@HEX: Brennan TFA catalog p.20 table TFA-p020-t01 "1501-FG MP-FPS 90 DEG ELBOW" row 1501-20-16-FG col "M1 LGTH" = "2.050" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 435.5, page verified True) [Brennan = yes 2026-10-18] - axis crossing to the swivel-nut face (column mapping: REPORT.md, table 1501); CHEX@HEX: Brennan TFA catalog p.20 table TFA-p020-t01 "1501-FG MP-FPS 90 DEG ELBOW" row 1501-20-16-FG col "C HEX" = "1.500" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 435.5, page verified True) [Brennan = yes 2026-10-18] - swivel nut hex (column mapping: REPORT.md, table 1501); C1HEX@HEX: Brennan TFA catalog p.20 table TFA-p020-t01 "1501-FG MP-FPS 90 DEG ELBOW" row 1501-20-16-FG col "Y FLATS" = "1.625" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 435.5, page verified True) [Brennan = yes 2026-10-18] - forged body flats (column mapping: REPORT.md, table 1501); D2@BORE: Brennan TFA catalog p.20 table TFA-p020-t01 "1501-FG MP-FPS 90 DEG ELBOW" row 1501-20-16-FG col "A1 DRILL" = "1.250" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 435.5, page verified True) [Brennan = yes 2026-10-18] - male NPTF end drill (column mapping: REPORT.md, table 1501); D@BORE: Brennan TFA catalog p.20 table TFA-p020-t01 "1501-FG MP-FPS 90 DEG ELBOW" row 1501-20-16-FG col "A2 DRILL" = "0.830" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 435.5, page verified True) [Brennan = yes 2026-10-18] - NPSM swivel stem bore (column mapping: REPORT.md, table 1501); THDMAJ_A@DRIVE: end library: pipe OD of the -20 NPTF thread = 1.66 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[20], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A1@DRIVE: end library: pipe OD of the -16 NPSM swivel thread = 1.315 (ASME B1.20.1 pipe OD, ms51500.py NPTF[16]; the value every built 1501 / 1405 / 1502 row carries for its NPSM end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Threads: thread callouts from the part number dashes in the format of the table's other rows; = Brennan TFA-p020-t01 thread columns (A1 NPTF 1-1/4-11-1/2, A2 NPSM 1-11-1/2) and OMi Items Side 1 / 2 / 3 Thread</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1501-20-16 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1501-20-16 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog, end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate)</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -3658,6 +3732,11 @@
       <c r="Q52" t="inlineStr">
         <is>
           <t>1501-20-16-FG</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>

--- a/04_DESIGN_TABLES/DesignTable_1501.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_1501.xlsx
@@ -796,7 +796,7 @@
         <v>0.28</v>
       </c>
       <c r="H7" t="n">
-        <v>0.23</v>
+        <v>0.13</v>
       </c>
       <c r="I7" t="n">
         <v>0.54</v>
@@ -821,12 +821,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Air-Way s113 only (double-pass 48 rows)</t>
+          <t>[BRENNAN-CELL 2026-10-20: D@BORE] Air-Way s113 only (double-pass 48 rows); D@BORE: Brennan TFA catalog p.20 table TFA-p020-t01 "MP-FPS 90 DEG ELBOW" row 1501-04-02-FG col "A2 DRILL" = 0.13 (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_index.json, page verified True) [user 2026-10-20 Q1: Air-Way value cannot be built -&gt; Brennan ("use brennans")] (Air-Way printed 0.23: the NPSM stem bore 0.23 is wider than the -02 stem tip (dia 0.234: neck wall 0.014); generator BLOCKED. Air-Way's own non-FG 1501-04-02 row prints 0.13 (this row's $COMMENT: "D printed 0.23 (sibling non-FG row 0.13)"))</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>D printed 0.23 (sibling non-FG row 0.13); copied as printed</t>
+          <t>D printed 0.23 (sibling non-FG row 0.13); copied as printed | 2026-10-20 D@BORE = Brennan 0.13 (Air-Way 0.23 cannot be built: the NPSM stem bore 0.23 is wider than the -02 stem tip (dia 0.234: neck wall 0.014); generator BLOCKED. Air-Way's own non-FG 1501-04-02 row prints 0.13 (this row's $COMMENT: "D printed 0.23 (sibling non-FG row 0.13)"))</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -837,6 +837,11 @@
       <c r="Q7" t="inlineStr">
         <is>
           <t>1501-04-02-FG</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3357,7 @@
         <v>2.19</v>
       </c>
       <c r="E47" t="n">
-        <v>1.88</v>
+        <v>2.125</v>
       </c>
       <c r="F47" t="n">
         <v>1.87</v>
@@ -3386,7 +3391,12 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>Air-Way s113 only (double-pass 48 rows)</t>
+          <t>[BRENNAN-CELL 2026-10-20: CHEX@HEX] Air-Way s113 only (double-pass 48 rows); CHEX@HEX: Brennan TFA catalog p.20 table TFA-p020-t01 "MP-FPS 90 DEG ELBOW" row 1501-24-24-FG col "C HEX" = 2.125 (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_index.json, page verified True) [user 2026-10-20 Q1: Air-Way value cannot be built -&gt; Brennan ("use brennans")] (Air-Way printed 1.88: the nut hex 1.88 is smaller than the Brennan -24 NPSM swivel nut (2.125) the generator's nut shape is measured from, and smaller than Air-Way's own non-FG 1501-24-24 nut (2.13); generator BLOCKED ("Air-Way nut hex C(2) 1.88 differs from the Brennan nut 2.125"))</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>2026-10-20 CHEX@HEX = Brennan 2.125 (Air-Way 1.88 cannot be built: the nut hex 1.88 is smaller than the Brennan -24 NPSM swivel nut (2.125) the generator's nut shape is measured from, and smaller than Air-Way's own non-FG 1501-24-24 nut (2.13); generator BLOCKED ("Air-Way nut hex C(2) 1.88 differs from the Brennan nut 2.125"))</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -3397,6 +3407,11 @@
       <c r="Q47" t="inlineStr">
         <is>
           <t>1501-24-24-FG</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
